--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,6 +887,536 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133622696</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brännåsen-Granndalen, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>334807</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6387241</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133622725</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brännåsen-Granndalen, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>334851</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6387262</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133622775</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Brännåsen-Granndalen, Hl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>334889</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6387268</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133622754</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79952</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brännåsen-Granndalen, Hl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>334851</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6387262</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133623855</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57136</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Brännåsen-Granndalen, Hl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>334766</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6387298</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>En tupp i sin hemvist respektive revir</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133622696</v>
+        <v>133622725</v>
       </c>
       <c r="B4" t="n">
         <v>57955</v>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334807</v>
+        <v>334851</v>
       </c>
       <c r="R4" t="n">
-        <v>6387241</v>
+        <v>6387262</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133622725</v>
+        <v>133622696</v>
       </c>
       <c r="B5" t="n">
         <v>57955</v>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>334851</v>
+        <v>334807</v>
       </c>
       <c r="R5" t="n">
-        <v>6387262</v>
+        <v>6387241</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133218929</v>
       </c>
       <c r="B2" t="n">
-        <v>97823</v>
+        <v>97825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133218532</v>
       </c>
       <c r="B3" t="n">
-        <v>91902</v>
+        <v>91904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>133622775</v>
       </c>
       <c r="B6" t="n">
-        <v>79952</v>
+        <v>79953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>133622754</v>
       </c>
       <c r="B7" t="n">
-        <v>79952</v>
+        <v>79953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133218929</v>
       </c>
       <c r="B2" t="n">
-        <v>97825</v>
+        <v>97833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133218532</v>
       </c>
       <c r="B3" t="n">
-        <v>91904</v>
+        <v>91912</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133622725</v>
+        <v>133622696</v>
       </c>
       <c r="B4" t="n">
         <v>57955</v>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334851</v>
+        <v>334807</v>
       </c>
       <c r="R4" t="n">
-        <v>6387262</v>
+        <v>6387241</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133622696</v>
+        <v>133622725</v>
       </c>
       <c r="B5" t="n">
         <v>57955</v>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>334807</v>
+        <v>334851</v>
       </c>
       <c r="R5" t="n">
-        <v>6387241</v>
+        <v>6387262</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133218929</v>
       </c>
       <c r="B2" t="n">
-        <v>97833</v>
+        <v>97861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133218532</v>
       </c>
       <c r="B3" t="n">
-        <v>91912</v>
+        <v>91931</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>133622696</v>
       </c>
       <c r="B4" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>133622725</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>133622775</v>
       </c>
       <c r="B6" t="n">
-        <v>79953</v>
+        <v>79967</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>133622754</v>
       </c>
       <c r="B7" t="n">
-        <v>79953</v>
+        <v>79967</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>133623855</v>
       </c>
       <c r="B8" t="n">
-        <v>57136</v>
+        <v>57143</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133622696</v>
+        <v>133622725</v>
       </c>
       <c r="B4" t="n">
         <v>57962</v>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334807</v>
+        <v>334851</v>
       </c>
       <c r="R4" t="n">
-        <v>6387241</v>
+        <v>6387262</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133622725</v>
+        <v>133622696</v>
       </c>
       <c r="B5" t="n">
         <v>57962</v>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>334851</v>
+        <v>334807</v>
       </c>
       <c r="R5" t="n">
-        <v>6387262</v>
+        <v>6387241</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133218929</v>
       </c>
       <c r="B2" t="n">
-        <v>97861</v>
+        <v>97871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133218532</v>
       </c>
       <c r="B3" t="n">
-        <v>91931</v>
+        <v>91941</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>133622725</v>
       </c>
       <c r="B4" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>133622696</v>
       </c>
       <c r="B5" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>133622775</v>
       </c>
       <c r="B6" t="n">
-        <v>79967</v>
+        <v>79977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>133622754</v>
       </c>
       <c r="B7" t="n">
-        <v>79967</v>
+        <v>79977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>133623855</v>
       </c>
       <c r="B8" t="n">
-        <v>57143</v>
+        <v>57153</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>133622775</v>
       </c>
       <c r="B6" t="n">
-        <v>79977</v>
+        <v>79978</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>133622754</v>
       </c>
       <c r="B7" t="n">
-        <v>79977</v>
+        <v>79978</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133622725</v>
+        <v>133622696</v>
       </c>
       <c r="B4" t="n">
         <v>57972</v>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334851</v>
+        <v>334807</v>
       </c>
       <c r="R4" t="n">
-        <v>6387262</v>
+        <v>6387241</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133622696</v>
+        <v>133622725</v>
       </c>
       <c r="B5" t="n">
         <v>57972</v>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>334807</v>
+        <v>334851</v>
       </c>
       <c r="R5" t="n">
-        <v>6387241</v>
+        <v>6387262</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133622696</v>
+        <v>133622725</v>
       </c>
       <c r="B4" t="n">
         <v>57972</v>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334807</v>
+        <v>334851</v>
       </c>
       <c r="R4" t="n">
-        <v>6387241</v>
+        <v>6387262</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133622725</v>
+        <v>133622696</v>
       </c>
       <c r="B5" t="n">
         <v>57972</v>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>334851</v>
+        <v>334807</v>
       </c>
       <c r="R5" t="n">
-        <v>6387262</v>
+        <v>6387241</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,7 +1102,7 @@
         <v>133622775</v>
       </c>
       <c r="B6" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>133622754</v>
       </c>
       <c r="B7" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>133218929</v>
       </c>
       <c r="B2" t="n">
-        <v>97871</v>
+        <v>97888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133218532</v>
       </c>
       <c r="B3" t="n">
-        <v>91941</v>
+        <v>91958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,53 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133622725</v>
+        <v>133221543</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>91958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>4660</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brännåsen-Granndalen, Hl</t>
+          <t>Berget Norr, Berget Norr, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334851</v>
+        <v>334847</v>
       </c>
       <c r="R4" t="n">
-        <v>6387262</v>
+        <v>6387341</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Mats Foss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Mats Foss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133622696</v>
+        <v>133220773</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1005,42 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brännåsen-Granndalen, Hl</t>
+          <t>Berget Norr, Berget Norr, Hl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>334807</v>
+        <v>334843</v>
       </c>
       <c r="R5" t="n">
-        <v>6387241</v>
+        <v>6387321</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,12 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,22 +1091,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Mats Foss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Mats Foss</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133622775</v>
+        <v>133622754</v>
       </c>
       <c r="B6" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1137,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>334889</v>
+        <v>334851</v>
       </c>
       <c r="R6" t="n">
-        <v>6387268</v>
+        <v>6387262</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133622754</v>
+        <v>133622775</v>
       </c>
       <c r="B7" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1238,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>334851</v>
+        <v>334889</v>
       </c>
       <c r="R7" t="n">
-        <v>6387262</v>
+        <v>6387268</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,27 +1305,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133623855</v>
+        <v>133622696</v>
       </c>
       <c r="B8" t="n">
-        <v>57153</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1329,22 +1333,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1352,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>334766</v>
+        <v>334807</v>
       </c>
       <c r="R8" t="n">
-        <v>6387298</v>
+        <v>6387241</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,11 +1386,6 @@
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>En tupp i sin hemvist respektive revir</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1416,6 +1407,229 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133622725</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Brännåsen-Granndalen, Hl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>334851</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6387262</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133623855</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57153</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Brännåsen-Granndalen, Hl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>334766</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6387298</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>En tupp i sin hemvist respektive revir</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133218929</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133218532</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133221543</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133220773</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133622754</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133622775</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133622696</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133622725</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,8 +1675,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133623855</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1678,6 +1678,118 @@
       <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/133623855</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135935558</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98138</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Granndalen, Granndalen, Hl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>334547</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6387168</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135935558</t>
         </is>
       </c>
     </row>
@@ -1692,6 +1804,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135935558</v>
       </c>
       <c r="B11" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135935558</v>
       </c>
       <c r="B11" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135935558</v>
       </c>
       <c r="B11" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135935558</v>
       </c>
       <c r="B11" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135935558</v>
       </c>
       <c r="B11" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135935558</v>
       </c>
       <c r="B11" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135935558</v>
       </c>
       <c r="B11" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135935558</v>
       </c>
       <c r="B11" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135935558</v>
       </c>
       <c r="B11" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135935558</v>
       </c>
       <c r="B11" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135935558</v>
       </c>
       <c r="B11" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
